--- a/config/Revisjonsliste.xlsx
+++ b/config/Revisjonsliste.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Revit\Python\Revit_BIM_Agnet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Revit\Python\Revit_BIM_Agent\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{040CD016-A7DE-411F-A8E9-3A282B6B37D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1EC037-9E4F-412C-B2E7-8C3E4BF1FE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="2100" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51480" yWindow="2100" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LPE161" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="9">
   <si>
     <t>FOB_Revisjonsdato</t>
   </si>
@@ -66,19 +66,28 @@
   </si>
   <si>
     <t>FIAA</t>
+  </si>
+  <si>
+    <t>2026.08.24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -106,12 +115,13 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -578,8 +588,8 @@
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -625,8 +635,8 @@
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -672,8 +682,8 @@
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
